--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487940_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487940_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5561</v>
+        <v>4.8088</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4623</v>
+        <v>2.9498</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0938</v>
+        <v>1.859</v>
       </c>
       <c r="G2" t="n">
         <v>1.7188</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5366</v>
+        <v>1.7892</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3075</v>
+        <v>1.795</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2291</v>
+        <v>-0.0058</v>
       </c>
       <c r="V2" t="n">
         <v>0.8845</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1065</v>
+        <v>4.7585</v>
       </c>
       <c r="E3" t="n">
-        <v>3.827</v>
+        <v>3.7431</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2796</v>
+        <v>1.0153</v>
       </c>
       <c r="G3" t="n">
         <v>3.4194</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2189</v>
+        <v>1.8708</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6583</v>
+        <v>1.5745</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5605</v>
+        <v>0.2963</v>
       </c>
       <c r="V3" t="n">
         <v>0.3007</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3857</v>
+        <v>1.9236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4538</v>
+        <v>0.0669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9318</v>
+        <v>1.8567</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.061</v>
+        <v>-1.4269</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.582</v>
+        <v>0.4794</v>
       </c>
       <c r="I4" t="n">
-        <v>1.521</v>
+        <v>-1.9063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2086</v>
+        <v>-1.8349</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6634</v>
+        <v>0.1123</v>
       </c>
       <c r="L4" t="n">
-        <v>1.872</v>
+        <v>-1.9472</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2696</v>
+        <v>0.408</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0814</v>
+        <v>0.3672</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.351</v>
+        <v>0.0408</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5403</v>
+        <v>0.6741</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8665</v>
+        <v>0.9611</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3261</v>
+        <v>-0.287</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5306999999999999</v>
+        <v>2.052</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4599</v>
+        <v>1.9813</v>
       </c>
       <c r="X4" t="n">
         <v>0.0708</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0705</v>
+        <v>1.2828</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8734</v>
+        <v>0.2629</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8029</v>
+        <v>1.0199</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4789</v>
+        <v>-0.061</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2431</v>
+        <v>-1.582</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.722</v>
+        <v>1.521</v>
       </c>
       <c r="J5" t="n">
-        <v>0.346</v>
+        <v>0.2086</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8229</v>
+        <v>-1.6634</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4769</v>
+        <v>1.872</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8248</v>
+        <v>-0.2696</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5798</v>
+        <v>0.0814</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.245</v>
+        <v>-0.351</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.488</v>
+        <v>1.4374</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4005</v>
+        <v>1.6755</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.2381</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6452</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3351</v>
+        <v>0.4599</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6899</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9637</v>
+        <v>1.0896</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5994</v>
+        <v>2.9806</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5631</v>
+        <v>-1.891</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4269</v>
+        <v>-1.4789</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4794</v>
+        <v>1.2431</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9063</v>
+        <v>-2.722</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8349</v>
+        <v>0.346</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1123</v>
+        <v>1.8229</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9472</v>
+        <v>-1.4769</v>
       </c>
       <c r="M6" t="n">
-        <v>0.408</v>
+        <v>-1.8248</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3672</v>
+        <v>-0.5798</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0408</v>
+        <v>-1.245</v>
       </c>
       <c r="P6" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.6244</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.6649</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.2857</v>
+        <v>0.5071</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2948</v>
+        <v>0.5077</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5806</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>2.052</v>
+        <v>1.6452</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9813</v>
+        <v>2.3351</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0708</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3566</v>
+        <v>0.5736</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.253</v>
+        <v>-1.801</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6095</v>
+        <v>2.3747</v>
       </c>
       <c r="G7" t="n">
         <v>0.0102</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2507</v>
+        <v>1.4678</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8787</v>
+        <v>1.3307</v>
       </c>
       <c r="U7" t="n">
-        <v>0.372</v>
+        <v>0.1371</v>
       </c>
       <c r="V7" t="n">
         <v>0.7607</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6612</v>
+        <v>-1.4763</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1716</v>
+        <v>1.386</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8329</v>
+        <v>-2.8622</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5478</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5911</v>
+        <v>-0.4061</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1833</v>
+        <v>0.031</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4077</v>
+        <v>-0.4371</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1061</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4351</v>
+        <v>-2.116</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6816</v>
+        <v>-0.3542</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7535</v>
+        <v>-1.7618</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2583</v>
+        <v>-0.2246</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7696</v>
+        <v>-0.5863</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0279</v>
+        <v>0.3617</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9338</v>
+        <v>0.9226</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1085</v>
+        <v>-0.2922</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1747</v>
+        <v>1.2148</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1921</v>
+        <v>-1.1472</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3389</v>
+        <v>-0.294</v>
       </c>
       <c r="O9" t="n">
         <v>-0.8532</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.2487</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2394</v>
+        <v>-0.0776</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4658</v>
+        <v>-0.0281</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2264</v>
+        <v>-0.0496</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.662</v>
+        <v>-2.4439</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.8959</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8792</v>
+        <v>-1.548</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2246</v>
+        <v>-0.2583</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5863</v>
+        <v>0.7696</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3617</v>
+        <v>-1.0279</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9226</v>
+        <v>0.9338</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2922</v>
+        <v>1.1085</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2148</v>
+        <v>-0.1747</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1472</v>
+        <v>-1.1921</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.294</v>
+        <v>-0.3389</v>
       </c>
       <c r="O10" t="n">
         <v>-0.8532</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6237</v>
+        <v>0.2306</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4567</v>
+        <v>0.2515</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.167</v>
+        <v>-0.0209</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8852</v>
+        <v>-6.9527</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5987</v>
+        <v>-4.813</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2865</v>
+        <v>-2.1397</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9267</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1226</v>
+        <v>0.0551</v>
       </c>
       <c r="T11" t="n">
-        <v>0.531</v>
+        <v>0.3167</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4084</v>
+        <v>-0.2616</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5838</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7956000000000003</v>
+        <v>1.448</v>
       </c>
       <c r="E12" t="n">
-        <v>2.872600000000001</v>
+        <v>3.525200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0772</v>
+        <v>-2.077100000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.775799999999999</v>
@@ -1366,10 +1366,10 @@
         <v>4.308399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4513</v>
+        <v>3.451300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8571000000000009</v>
+        <v>0.8571000000000006</v>
       </c>
       <c r="M12" t="n">
         <v>-7.0841</v>
@@ -1381,7 +1381,7 @@
         <v>-6.021</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.243499999999999</v>
+        <v>-6.2435</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.6901</v>
@@ -1390,19 +1390,19 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>6.895999999999999</v>
+        <v>7.5484</v>
       </c>
       <c r="T12" t="n">
-        <v>7.763100000000001</v>
+        <v>8.415600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8671000000000001</v>
+        <v>-0.8673</v>
       </c>
       <c r="V12" t="n">
-        <v>2.9189</v>
+        <v>2.918899999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>8.491099999999999</v>
+        <v>8.491100000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-5.5722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5281</v>
+        <v>4.1099</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6289</v>
+        <v>1.9503</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8992</v>
+        <v>2.1596</v>
       </c>
       <c r="G13" t="n">
         <v>1.8199</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0399</v>
+        <v>-0.4581</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4443</v>
+        <v>-0.1228</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5956</v>
+        <v>-0.3353</v>
       </c>
       <c r="V13" t="n">
         <v>1.2914</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3159</v>
+        <v>3.4817</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5225</v>
+        <v>2.6296</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7934</v>
+        <v>0.8521</v>
       </c>
       <c r="G14" t="n">
         <v>2.991</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9238</v>
+        <v>-0.7579</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>-0.6105</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2061</v>
+        <v>-0.1474</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0559</v>
+        <v>1.3631</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1735</v>
+        <v>1.3162</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1175</v>
+        <v>0.0469</v>
       </c>
       <c r="G15" t="n">
         <v>1.4764</v>
@@ -1624,13 +1624,13 @@
         <v>2.4974</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4359</v>
+        <v>0.7431</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3073</v>
+        <v>0.4501</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1286</v>
+        <v>0.293</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1051</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9107</v>
+        <v>0.9376</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7651</v>
+        <v>1.4436</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8544</v>
+        <v>-0.506</v>
       </c>
       <c r="G16" t="n">
         <v>0.6855</v>
@@ -1702,13 +1702,13 @@
         <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1522</v>
+        <v>-1.1252</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2544</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4065</v>
+        <v>-1.0581</v>
       </c>
       <c r="V16" t="n">
         <v>0.5449000000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6425</v>
+        <v>0.3902</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1597</v>
+        <v>-0.2342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4828</v>
+        <v>0.6244</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6374</v>
+        <v>0.1821</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4546</v>
+        <v>0.1429</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1829</v>
+        <v>0.0392</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0208</v>
+        <v>0.0392</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2951</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2743</v>
+        <v>0.0392</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6166</v>
+        <v>0.1429</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1595</v>
+        <v>0.1429</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4572</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4823</v>
+        <v>-0.2081</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2794</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7971</v>
+        <v>-0.1429</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4104</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0177</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3902</v>
+        <v>-0.0868</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2342</v>
+        <v>-0.1616</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6244</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1821</v>
+        <v>0.2117</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1429</v>
+        <v>-2.9234</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0392</v>
+        <v>3.1351</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0392</v>
+        <v>0.8651</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-2.4781</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0392</v>
+        <v>3.3432</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1429</v>
+        <v>-0.6534</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1429</v>
+        <v>-0.4452</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.2082</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2081</v>
+        <v>-0.3844</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.3677</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1429</v>
+        <v>-0.7522</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3927</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3203</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9117</v>
+        <v>-1.2333</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4086</v>
+        <v>0.5846</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2117</v>
+        <v>-0.6374</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9234</v>
+        <v>-0.4546</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1351</v>
+        <v>-0.1829</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8651</v>
+        <v>-0.0208</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.4781</v>
+        <v>-0.2951</v>
       </c>
       <c r="L19" t="n">
-        <v>3.3432</v>
+        <v>0.2743</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6534</v>
+        <v>-0.6166</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4452</v>
+        <v>-0.1595</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2082</v>
+        <v>-0.4572</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.618</v>
+        <v>0.191</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3824</v>
+        <v>0.8864</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2356</v>
+        <v>-0.6954</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.4104</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3538</v>
+        <v>-0.0177</v>
       </c>
       <c r="X19" t="n">
         <v>-0.3927</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1356</v>
+        <v>-1.0831</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1669</v>
+        <v>-0.6311</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9687</v>
+        <v>-0.452</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1425</v>
@@ -2014,13 +2014,13 @@
         <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1653</v>
+        <v>-1.1129</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.721</v>
+        <v>-0.1852</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4444</v>
+        <v>-0.9277</v>
       </c>
       <c r="V20" t="n">
         <v>2.7561</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.198</v>
+        <v>-3.1226</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7997</v>
+        <v>-1.0141</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3982</v>
+        <v>-2.1086</v>
       </c>
       <c r="G21" t="n">
         <v>-0.06320000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0078</v>
+        <v>0.0675</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4658</v>
+        <v>0.2515</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4736</v>
+        <v>-0.184</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9188</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.985</v>
+        <v>-3.2793</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0601</v>
+        <v>-1.9885</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9249</v>
+        <v>-1.2908</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7476</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.699</v>
+        <v>-0.9933</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1091</v>
+        <v>-0.0376</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5899</v>
+        <v>-0.9557</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3303</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7956000000000012</v>
+        <v>2.061999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0771</v>
+        <v>2.0769</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8725</v>
+        <v>-0.01499999999999968</v>
       </c>
       <c r="G23" t="n">
         <v>2.7759</v>
@@ -2218,10 +2218,10 @@
         <v>-2.3883</v>
       </c>
       <c r="I23" t="n">
-        <v>5.164</v>
+        <v>5.164000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>7.0842</v>
+        <v>7.084200000000001</v>
       </c>
       <c r="K23" t="n">
         <v>1.0631</v>
@@ -2248,13 +2248,13 @@
         <v>17.6901</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.895899999999999</v>
+        <v>-4.0383</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8672</v>
+        <v>0.8673000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.763100000000001</v>
+        <v>-4.9057</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9187</v>
